--- a/ANm/Eor_Maize_results.xlsx
+++ b/ANm/Eor_Maize_results.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,32 +417,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>SOC Baseline (t/ha)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>SOC Project (t/ha)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SOC Difference (t/ha)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Delta SOC (t/ha)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ERs (tCO2e/ha)</t>
         </is>
@@ -481,19 +469,19 @@
         <v>2026</v>
       </c>
       <c r="B3" t="n">
-        <v>100.9850422916091</v>
+        <v>105.7579059580901</v>
       </c>
       <c r="C3" t="n">
         <v>113.9409026286368</v>
       </c>
       <c r="D3" t="n">
-        <v>12.95586033702773</v>
+        <v>8.182996670546729</v>
       </c>
       <c r="E3" t="n">
-        <v>12.95731426462511</v>
+        <v>8.18445059814411</v>
       </c>
       <c r="F3" t="n">
-        <v>47.51015230362541</v>
+        <v>30.00965219319507</v>
       </c>
     </row>
     <row r="4">
@@ -501,19 +489,19 @@
         <v>2027</v>
       </c>
       <c r="B4" t="n">
-        <v>93.64038672410013</v>
+        <v>101.124826615053</v>
       </c>
       <c r="C4" t="n">
         <v>113.9409017419045</v>
       </c>
       <c r="D4" t="n">
-        <v>20.30051501780433</v>
+        <v>12.81607512685142</v>
       </c>
       <c r="E4" t="n">
-        <v>7.3446546807766</v>
+        <v>4.633078456304688</v>
       </c>
       <c r="F4" t="n">
-        <v>26.93040049618087</v>
+        <v>16.98795433978385</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +509,19 @@
         <v>2028</v>
       </c>
       <c r="B5" t="n">
-        <v>88.62153963636349</v>
+        <v>97.96833244919088</v>
       </c>
       <c r="C5" t="n">
         <v>113.9409009003157</v>
       </c>
       <c r="D5" t="n">
-        <v>25.31936126395219</v>
+        <v>15.9725684511248</v>
       </c>
       <c r="E5" t="n">
-        <v>5.018846246147859</v>
+        <v>3.156493324273384</v>
       </c>
       <c r="F5" t="n">
-        <v>18.40243623587548</v>
+        <v>11.57380885566908</v>
       </c>
     </row>
     <row r="6">
@@ -541,19 +529,19 @@
         <v>2029</v>
       </c>
       <c r="B6" t="n">
-        <v>84.86030646354129</v>
+        <v>95.61398738104573</v>
       </c>
       <c r="C6" t="n">
         <v>113.9409001015723</v>
       </c>
       <c r="D6" t="n">
-        <v>29.08059363803102</v>
+        <v>18.32691272052658</v>
       </c>
       <c r="E6" t="n">
-        <v>3.76123237407883</v>
+        <v>2.354344269401778</v>
       </c>
       <c r="F6" t="n">
-        <v>13.79118537162238</v>
+        <v>8.632595654473187</v>
       </c>
     </row>
     <row r="7">
@@ -561,19 +549,19 @@
         <v>2030</v>
       </c>
       <c r="B7" t="n">
-        <v>81.80275339576531</v>
+        <v>93.7116142620401</v>
       </c>
       <c r="C7" t="n">
         <v>113.940899343493</v>
       </c>
       <c r="D7" t="n">
-        <v>32.13814594772768</v>
+        <v>20.22928508145289</v>
       </c>
       <c r="E7" t="n">
-        <v>3.057552309696661</v>
+        <v>1.902372360926307</v>
       </c>
       <c r="F7" t="n">
-        <v>11.21102513555442</v>
+        <v>6.97536532339646</v>
       </c>
     </row>
     <row r="8">
@@ -581,19 +569,19 @@
         <v>2031</v>
       </c>
       <c r="B8" t="n">
-        <v>79.15802760063035</v>
+        <v>92.0769819164165</v>
       </c>
       <c r="C8" t="n">
         <v>113.9408986240075</v>
       </c>
       <c r="D8" t="n">
-        <v>34.78287102337717</v>
+        <v>21.86391670759102</v>
       </c>
       <c r="E8" t="n">
-        <v>2.64472507564949</v>
+        <v>1.63463162613813</v>
       </c>
       <c r="F8" t="n">
-        <v>9.697325277381461</v>
+        <v>5.993649295839812</v>
       </c>
     </row>
     <row r="9">
@@ -601,19 +589,19 @@
         <v>2032</v>
       </c>
       <c r="B9" t="n">
-        <v>76.77178284400739</v>
+        <v>90.61201963604501</v>
       </c>
       <c r="C9" t="n">
         <v>113.9408979411511</v>
       </c>
       <c r="D9" t="n">
-        <v>37.16911509714375</v>
+        <v>23.32887830510613</v>
       </c>
       <c r="E9" t="n">
-        <v>2.386244073766576</v>
+        <v>1.464961597515114</v>
       </c>
       <c r="F9" t="n">
-        <v>8.749561603810781</v>
+        <v>5.371525857555416</v>
       </c>
     </row>
     <row r="10">
@@ -621,19 +609,19 @@
         <v>2033</v>
       </c>
       <c r="B10" t="n">
-        <v>74.5611056822072</v>
+        <v>89.26378310435763</v>
       </c>
       <c r="C10" t="n">
         <v>113.940897293059</v>
       </c>
       <c r="D10" t="n">
-        <v>39.3797916108518</v>
+        <v>24.67711418870137</v>
       </c>
       <c r="E10" t="n">
-        <v>2.210676513708052</v>
+        <v>1.348235883595237</v>
       </c>
       <c r="F10" t="n">
-        <v>8.105813883596189</v>
+        <v>4.943531573182535</v>
       </c>
     </row>
     <row r="11">
@@ -641,19 +629,19 @@
         <v>2034</v>
       </c>
       <c r="B11" t="n">
-        <v>72.48066596968599</v>
+        <v>88.00309853630083</v>
       </c>
       <c r="C11" t="n">
         <v>113.9408966779613</v>
       </c>
       <c r="D11" t="n">
-        <v>41.46023070827528</v>
+        <v>25.93779814166044</v>
       </c>
       <c r="E11" t="n">
-        <v>2.080439097423479</v>
+        <v>1.26068395295907</v>
       </c>
       <c r="F11" t="n">
-        <v>7.628276690552757</v>
+        <v>4.62250782751659</v>
       </c>
     </row>
     <row r="12">
@@ -661,19 +649,19 @@
         <v>2035</v>
       </c>
       <c r="B12" t="n">
-        <v>70.5049904253062</v>
+        <v>86.81337203047835</v>
       </c>
       <c r="C12" t="n">
         <v>113.9408960941782</v>
       </c>
       <c r="D12" t="n">
-        <v>43.43590566887201</v>
+        <v>27.12752406369987</v>
       </c>
       <c r="E12" t="n">
-        <v>1.975674960596734</v>
+        <v>1.189725922039429</v>
       </c>
       <c r="F12" t="n">
-        <v>7.244141522188026</v>
+        <v>4.362328380811239</v>
       </c>
     </row>
     <row r="13">
@@ -681,19 +669,19 @@
         <v>2036</v>
       </c>
       <c r="B13" t="n">
-        <v>68.61914320508133</v>
+        <v>85.68470210454399</v>
       </c>
       <c r="C13" t="n">
         <v>113.9408955401156</v>
       </c>
       <c r="D13" t="n">
-        <v>45.32175233503425</v>
+        <v>28.25619343557159</v>
       </c>
       <c r="E13" t="n">
-        <v>1.885846666162237</v>
+        <v>1.128669371871723</v>
       </c>
       <c r="F13" t="n">
-        <v>6.914771109261537</v>
+        <v>4.138454363529651</v>
       </c>
     </row>
     <row r="14">
@@ -701,19 +689,19 @@
         <v>2037</v>
       </c>
       <c r="B14" t="n">
-        <v>66.81381447891405</v>
+        <v>84.61077443842532</v>
       </c>
       <c r="C14" t="n">
         <v>113.9408950142603</v>
       </c>
       <c r="D14" t="n">
-        <v>47.12708053534627</v>
+        <v>29.330120575835</v>
       </c>
       <c r="E14" t="n">
-        <v>1.805328200312019</v>
+        <v>1.073927140263407</v>
       </c>
       <c r="F14" t="n">
-        <v>6.619536734477403</v>
+        <v>3.937732847632494</v>
       </c>
     </row>
     <row r="15">
@@ -721,19 +709,19 @@
         <v>2038</v>
       </c>
       <c r="B15" t="n">
-        <v>65.0827275021631</v>
+        <v>83.58722088368448</v>
       </c>
       <c r="C15" t="n">
         <v>113.9408945151764</v>
       </c>
       <c r="D15" t="n">
-        <v>48.85816701301327</v>
+        <v>30.35367363149189</v>
       </c>
       <c r="E15" t="n">
-        <v>1.731086477667006</v>
+        <v>1.02355305565689</v>
       </c>
       <c r="F15" t="n">
-        <v>6.347317084779021</v>
+        <v>3.753027870741931</v>
       </c>
     </row>
     <row r="16">
@@ -741,19 +729,19 @@
         <v>2039</v>
       </c>
       <c r="B16" t="n">
-        <v>63.42126736774041</v>
+        <v>82.61075052675899</v>
       </c>
       <c r="C16" t="n">
         <v>113.9408940415008</v>
       </c>
       <c r="D16" t="n">
-        <v>50.51962667376038</v>
+        <v>31.33014351474181</v>
       </c>
       <c r="E16" t="n">
-        <v>1.661459660747113</v>
+        <v>0.9764698832499192</v>
       </c>
       <c r="F16" t="n">
-        <v>6.092018756072747</v>
+        <v>3.580389571916371</v>
       </c>
     </row>
     <row r="17">
@@ -761,19 +749,19 @@
         <v>2040</v>
       </c>
       <c r="B17" t="n">
-        <v>61.82575421357108</v>
+        <v>81.67868829282116</v>
       </c>
       <c r="C17" t="n">
         <v>113.9408935919401</v>
       </c>
       <c r="D17" t="n">
-        <v>52.11513937836904</v>
+        <v>32.26220529911896</v>
       </c>
       <c r="E17" t="n">
-        <v>1.595512704608659</v>
+        <v>0.9320617843771544</v>
       </c>
       <c r="F17" t="n">
-        <v>5.850213250231749</v>
+        <v>3.417559876049566</v>
       </c>
     </row>
     <row r="18">
@@ -781,19 +769,19 @@
         <v>2041</v>
       </c>
       <c r="B18" t="n">
-        <v>60.29305666030388</v>
+        <v>80.7887288577878</v>
       </c>
       <c r="C18" t="n">
         <v>113.9408931652666</v>
       </c>
       <c r="D18" t="n">
-        <v>53.64783650496272</v>
+        <v>33.1521643074788</v>
       </c>
       <c r="E18" t="n">
-        <v>1.532697126593675</v>
+        <v>0.8899590083598383</v>
       </c>
       <c r="F18" t="n">
-        <v>5.619889464176808</v>
+        <v>3.263183030652741</v>
       </c>
     </row>
     <row r="19">
@@ -801,19 +789,19 @@
         <v>2042</v>
       </c>
       <c r="B19" t="n">
-        <v>58.82038500064743</v>
+        <v>79.9388044045014</v>
       </c>
       <c r="C19" t="n">
         <v>113.940892760315</v>
       </c>
       <c r="D19" t="n">
-        <v>55.12050775966759</v>
+        <v>34.00208835581363</v>
       </c>
       <c r="E19" t="n">
-        <v>1.472671254704871</v>
+        <v>0.8499240483348274</v>
       </c>
       <c r="F19" t="n">
-        <v>5.399794600584525</v>
+        <v>3.1163881772277</v>
       </c>
     </row>
     <row r="20">
@@ -821,19 +809,19 @@
         <v>2043</v>
       </c>
       <c r="B20" t="n">
-        <v>57.4051794425265</v>
+        <v>79.12701263976278</v>
       </c>
       <c r="C20" t="n">
         <v>113.9408923759796</v>
       </c>
       <c r="D20" t="n">
-        <v>56.53571293345308</v>
+        <v>34.8138797362168</v>
       </c>
       <c r="E20" t="n">
-        <v>1.415205173785495</v>
+        <v>0.8117913804031787</v>
       </c>
       <c r="F20" t="n">
-        <v>5.189085637213481</v>
+        <v>2.976568394811655</v>
       </c>
     </row>
     <row r="21">
@@ -841,19 +829,19 @@
         <v>2044</v>
       </c>
       <c r="B21" t="n">
-        <v>56.04504868671584</v>
+        <v>78.3515767636176</v>
       </c>
       <c r="C21" t="n">
         <v>113.9408920112107</v>
       </c>
       <c r="D21" t="n">
-        <v>57.89584332449483</v>
+        <v>35.58931524759308</v>
       </c>
       <c r="E21" t="n">
-        <v>1.36013039104175</v>
+        <v>0.7754355113762728</v>
       </c>
       <c r="F21" t="n">
-        <v>4.987144767153083</v>
+        <v>2.843263541713</v>
       </c>
     </row>
     <row r="22">
@@ -861,19 +849,19 @@
         <v>2045</v>
       </c>
       <c r="B22" t="n">
-        <v>54.73773521932424</v>
+        <v>77.61082242954544</v>
       </c>
       <c r="C22" t="n">
         <v>113.9408916650122</v>
       </c>
       <c r="D22" t="n">
-        <v>59.20315644568797</v>
+        <v>36.33006923546677</v>
       </c>
       <c r="E22" t="n">
-        <v>1.307313121193133</v>
+        <v>0.7407539878736884</v>
       </c>
       <c r="F22" t="n">
-        <v>4.793481444374819</v>
+        <v>2.716097955536858</v>
       </c>
     </row>
     <row r="23">
@@ -881,19 +869,19 @@
         <v>2046</v>
       </c>
       <c r="B23" t="n">
-        <v>53.48109483852064</v>
+        <v>76.90316378458085</v>
       </c>
       <c r="C23" t="n">
         <v>113.9408913364387</v>
       </c>
       <c r="D23" t="n">
-        <v>60.45979649791806</v>
+        <v>37.03772755185784</v>
       </c>
       <c r="E23" t="n">
-        <v>1.25664005223009</v>
+        <v>0.7076583163910755</v>
       </c>
       <c r="F23" t="n">
-        <v>4.607680191510329</v>
+        <v>2.59474716010061</v>
       </c>
     </row>
     <row r="24">
@@ -901,19 +889,19 @@
         <v>2047</v>
       </c>
       <c r="B24" t="n">
-        <v>52.27308381666764</v>
+        <v>76.22709440334387</v>
       </c>
       <c r="C24" t="n">
         <v>113.9408910245929</v>
       </c>
       <c r="D24" t="n">
-        <v>61.66780720792525</v>
+        <v>37.71379662124902</v>
       </c>
       <c r="E24" t="n">
-        <v>1.208010710007194</v>
+        <v>0.6760690693911755</v>
       </c>
       <c r="F24" t="n">
-        <v>4.429372603359712</v>
+        <v>2.478919921100977</v>
       </c>
     </row>
     <row r="25">
@@ -921,19 +909,19 @@
         <v>2048</v>
       </c>
       <c r="B25" t="n">
-        <v>51.11175020540319</v>
+        <v>75.58118089835075</v>
       </c>
       <c r="C25" t="n">
         <v>113.9408907286231</v>
       </c>
       <c r="D25" t="n">
-        <v>62.82914052321996</v>
+        <v>38.35970983027239</v>
       </c>
       <c r="E25" t="n">
-        <v>1.161333315294705</v>
+        <v>0.6459132090233766</v>
       </c>
       <c r="F25" t="n">
-        <v>4.258222156080585</v>
+        <v>2.368348433085714</v>
       </c>
     </row>
     <row r="26">
@@ -941,19 +929,19 @@
         <v>2049</v>
       </c>
       <c r="B26" t="n">
-        <v>49.99522743217128</v>
+        <v>74.96405802938669</v>
       </c>
       <c r="C26" t="n">
         <v>113.9408904477213</v>
       </c>
       <c r="D26" t="n">
-        <v>63.94566301555003</v>
+        <v>38.97683241833462</v>
       </c>
       <c r="E26" t="n">
-        <v>1.116522492330077</v>
+        <v>0.6171225880622302</v>
       </c>
       <c r="F26" t="n">
-        <v>4.093915805210282</v>
+        <v>2.262782822894844</v>
       </c>
     </row>
     <row r="27">
@@ -961,19 +949,19 @@
         <v>2050</v>
       </c>
       <c r="B27" t="n">
-        <v>48.9217292038261</v>
+        <v>74.37442468482681</v>
       </c>
       <c r="C27" t="n">
         <v>113.9408901811202</v>
       </c>
       <c r="D27" t="n">
-        <v>65.01916097729406</v>
+        <v>39.56646549629336</v>
       </c>
       <c r="E27" t="n">
-        <v>1.073497961744032</v>
+        <v>0.5896330779587373</v>
       </c>
       <c r="F27" t="n">
-        <v>3.936159193061449</v>
+        <v>2.16198795251537</v>
       </c>
     </row>
     <row r="28">
@@ -981,19 +969,19 @@
         <v>2051</v>
       </c>
       <c r="B28" t="n">
-        <v>47.88954519136558</v>
+        <v>73.81104039881379</v>
       </c>
       <c r="C28" t="n">
         <v>113.9408899280917</v>
       </c>
       <c r="D28" t="n">
-        <v>66.05134473672615</v>
+        <v>40.12984952927795</v>
       </c>
       <c r="E28" t="n">
-        <v>1.032183759432087</v>
+        <v>0.5633840329845867</v>
       </c>
       <c r="F28" t="n">
-        <v>3.784673784584319</v>
+        <v>2.065741454276818</v>
       </c>
     </row>
     <row r="29">
@@ -1001,19 +989,19 @@
         <v>2052</v>
       </c>
       <c r="B29" t="n">
-        <v>46.8970372124102</v>
+        <v>73.27272222229996</v>
       </c>
       <c r="C29" t="n">
         <v>113.9408896879449</v>
       </c>
       <c r="D29" t="n">
-        <v>67.04385247553475</v>
+        <v>40.66816746564498</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9925077388085981</v>
+        <v>0.5383179363670365</v>
       </c>
       <c r="F29" t="n">
-        <v>3.639195042298193</v>
+        <v>1.973832433345801</v>
       </c>
     </row>
     <row r="30">
@@ -1021,19 +1009,19 @@
         <v>2053</v>
       </c>
       <c r="B30" t="n">
-        <v>45.94263575655612</v>
+        <v>72.75834184768532</v>
       </c>
       <c r="C30" t="n">
         <v>113.9408894600241</v>
       </c>
       <c r="D30" t="n">
-        <v>67.99825370346798</v>
+        <v>41.18254761233878</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9544012279332321</v>
+        <v>0.5143801466937958</v>
       </c>
       <c r="F30" t="n">
-        <v>3.499471169088518</v>
+        <v>1.886060537877251</v>
       </c>
     </row>
     <row r="31">
@@ -1041,19 +1029,19 @@
         <v>2054</v>
       </c>
       <c r="B31" t="n">
-        <v>45.02483676697778</v>
+        <v>72.2668229302415</v>
       </c>
       <c r="C31" t="n">
         <v>113.9408892437067</v>
       </c>
       <c r="D31" t="n">
-        <v>68.91605247672888</v>
+        <v>41.67406631346516</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9177987732608983</v>
+        <v>0.4915187011263811</v>
       </c>
       <c r="F31" t="n">
-        <v>3.365262168623294</v>
+        <v>1.802235237463397</v>
       </c>
     </row>
     <row r="32">
@@ -1061,19 +1049,19 @@
         <v>2055</v>
       </c>
       <c r="B32" t="n">
-        <v>44.14219862803962</v>
+        <v>71.7971385727276</v>
       </c>
       <c r="C32" t="n">
         <v>113.9408890384019</v>
       </c>
       <c r="D32" t="n">
-        <v>69.7986904103623</v>
+        <v>42.14375046567432</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8826379336334185</v>
+        <v>0.4696841522091546</v>
       </c>
       <c r="F32" t="n">
-        <v>3.236339089989201</v>
+        <v>1.7221752247669</v>
       </c>
     </row>
     <row r="33">
@@ -1081,19 +1069,19 @@
         <v>2056</v>
       </c>
       <c r="B33" t="n">
-        <v>43.29333932820472</v>
+        <v>71.34830895210362</v>
       </c>
       <c r="C33" t="n">
         <v>113.9408888435493</v>
       </c>
       <c r="D33" t="n">
-        <v>70.64754951534456</v>
+        <v>42.59257989144567</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8488591049822674</v>
+        <v>0.4488294257713505</v>
       </c>
       <c r="F33" t="n">
-        <v>3.11248338493498</v>
+        <v>1.645707894494952</v>
       </c>
     </row>
     <row r="34">
@@ -1101,19 +1089,19 @@
         <v>2057</v>
       </c>
       <c r="B34" t="n">
-        <v>42.47693377812877</v>
+        <v>70.9193990740677</v>
       </c>
       <c r="C34" t="n">
         <v>113.9408886586166</v>
       </c>
       <c r="D34" t="n">
-        <v>71.46395488048788</v>
+        <v>43.02148958454895</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8164053651433107</v>
+        <v>0.4289096931032788</v>
       </c>
       <c r="F34" t="n">
-        <v>2.993486338858806</v>
+        <v>1.572668874712022</v>
       </c>
     </row>
     <row r="35">
@@ -1121,19 +1109,19 @@
         <v>2058</v>
       </c>
       <c r="B35" t="n">
-        <v>41.69171126968997</v>
+        <v>70.50951664494586</v>
       </c>
       <c r="C35" t="n">
         <v>113.9408884830989</v>
       </c>
       <c r="D35" t="n">
-        <v>72.24917721340896</v>
+        <v>43.43137183815307</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7852223329210801</v>
+        <v>0.409882253604124</v>
       </c>
       <c r="F35" t="n">
-        <v>2.87914855404396</v>
+        <v>1.502901596548455</v>
       </c>
     </row>
     <row r="36">
@@ -1141,19 +1129,19 @@
         <v>2059</v>
       </c>
       <c r="B36" t="n">
-        <v>40.93645306504443</v>
+        <v>70.11781005265738</v>
       </c>
       <c r="C36" t="n">
         <v>113.9408883165168</v>
       </c>
       <c r="D36" t="n">
-        <v>73.0044352514724</v>
+        <v>43.82307826385946</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7552580380634453</v>
+        <v>0.3917064257063885</v>
       </c>
       <c r="F36" t="n">
-        <v>2.769279472899299</v>
+        <v>1.436256894256758</v>
       </c>
     </row>
     <row r="37">
@@ -1161,19 +1149,19 @@
         <v>2060</v>
       </c>
       <c r="B37" t="n">
-        <v>40.20999010678506</v>
+        <v>69.74346644980744</v>
       </c>
       <c r="C37" t="n">
         <v>113.9408881584154</v>
       </c>
       <c r="D37" t="n">
-        <v>73.73089805163032</v>
+        <v>44.19742170860793</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7264628001579183</v>
+        <v>0.3743434447484759</v>
       </c>
       <c r="F37" t="n">
-        <v>2.663696933912367</v>
+        <v>1.372592630744412</v>
       </c>
     </row>
     <row r="38">
@@ -1181,19 +1169,19 @@
         <v>2061</v>
       </c>
       <c r="B38" t="n">
-        <v>39.51120084153909</v>
+        <v>69.38570993282218</v>
       </c>
       <c r="C38" t="n">
         <v>113.9408880083629</v>
       </c>
       <c r="D38" t="n">
-        <v>74.42968716682381</v>
+        <v>44.55517807554072</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6987891151934917</v>
+        <v>0.3577563669327901</v>
       </c>
       <c r="F38" t="n">
-        <v>2.56222675570947</v>
+        <v>1.31177334542023</v>
       </c>
     </row>
     <row r="39">
@@ -1201,19 +1189,19 @@
         <v>2062</v>
       </c>
       <c r="B39" t="n">
-        <v>38.83900915019501</v>
+        <v>69.04379981164223</v>
       </c>
       <c r="C39" t="n">
         <v>113.9408878659496</v>
       </c>
       <c r="D39" t="n">
-        <v>75.10187871575462</v>
+        <v>44.8970880543074</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6721915489308117</v>
+        <v>0.3419099787666795</v>
       </c>
       <c r="F39" t="n">
-        <v>2.464702346079643</v>
+        <v>1.253669922144492</v>
       </c>
     </row>
     <row r="40">
@@ -1221,19 +1209,19 @@
         <v>2063</v>
       </c>
       <c r="B40" t="n">
-        <v>38.19238237858039</v>
+        <v>68.71702896494796</v>
       </c>
       <c r="C40" t="n">
         <v>113.9408877307867</v>
       </c>
       <c r="D40" t="n">
-        <v>75.74850535220627</v>
+        <v>45.2238587658387</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6466266364516429</v>
+        <v>0.3267707115312959</v>
       </c>
       <c r="F40" t="n">
-        <v>2.370964333656024</v>
+        <v>1.198159275614752</v>
       </c>
     </row>
     <row r="41">
@@ -1241,19 +1229,19 @@
         <v>2064</v>
       </c>
       <c r="B41" t="n">
-        <v>37.57032946290803</v>
+        <v>68.40472227625679</v>
       </c>
       <c r="C41" t="n">
         <v>113.9408876025048</v>
       </c>
       <c r="D41" t="n">
-        <v>76.3705581395968</v>
+        <v>45.53616532624802</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6220527873905297</v>
+        <v>0.3123065604093256</v>
       </c>
       <c r="F41" t="n">
-        <v>2.280860220431942</v>
+        <v>1.145124054834194</v>
       </c>
     </row>
     <row r="42">
@@ -1261,19 +1249,19 @@
         <v>2065</v>
       </c>
       <c r="B42" t="n">
-        <v>36.97189914472486</v>
+        <v>68.10623514654802</v>
       </c>
       <c r="C42" t="n">
         <v>113.9408874807538</v>
       </c>
       <c r="D42" t="n">
-        <v>76.96898833602893</v>
+        <v>45.83465233420577</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5984301964321332</v>
+        <v>0.2984870079577462</v>
       </c>
       <c r="F42" t="n">
-        <v>2.194244053584489</v>
+        <v>1.094452362511736</v>
       </c>
     </row>
   </sheetData>
